--- a/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE104"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13792,6 +13792,272 @@
       </c>
       <c r="AE104" t="n">
         <v>2.66</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BW-2026-110</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BW260059</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Gohar Yasakhanian</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>50×36×45cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0.081 CBM</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>20</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T105" t="n">
+        <v>456800</v>
+      </c>
+      <c r="U105" t="n">
+        <v>376000</v>
+      </c>
+      <c r="V105" t="n">
+        <v>80800</v>
+      </c>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>10571 Horse Creek Ave Shadow Hills CA 91040</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>1 (818) 667-7794</t>
+        </is>
+      </c>
+      <c r="AC105" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BW-2026-111</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BW260060</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Laura Swann</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>5 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>49.5×38.5×47.5cm(1CTN) / 55×36×18cm(1CTN) / 49×36.5×22.5cm(3CTN)</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0.247 CBM</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>58</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T106" t="n">
+        <v>1324720</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1289000</v>
+      </c>
+      <c r="V106" t="n">
+        <v>35720</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>"4170 Blackheath Dr Bartlett, TN 38135"</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>(901) 503‑8919</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>57.34</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE106"/>
+  <dimension ref="A1:AE107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14058,6 +14058,139 @@
       </c>
       <c r="AE106" t="n">
         <v>57.34</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BW-2026-112</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BW260061</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>54×24×28cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0.036 CBM</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>8</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T107" t="n">
+        <v>182720</v>
+      </c>
+      <c r="U107" t="n">
+        <v>150400</v>
+      </c>
+      <c r="V107" t="n">
+        <v>32320</v>
+      </c>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>8620 SAN Gabriel Drive LAREDO, TEXAS 78045</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>19563493361</t>
+        </is>
+      </c>
+      <c r="AC107" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>4.44</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>318720</v>
+        <v>326720</v>
       </c>
       <c r="U94" t="n">
         <v>185000</v>
       </c>
       <c r="V94" t="n">
-        <v>133720</v>
+        <v>141720</v>
       </c>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr">
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="T102" t="n">
-        <v>239040</v>
+        <v>255040</v>
       </c>
       <c r="U102" t="n">
         <v>135000</v>
       </c>
       <c r="V102" t="n">
-        <v>104040</v>
+        <v>120040</v>
       </c>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
@@ -13605,10 +13605,10 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -13621,13 +13621,13 @@
         </is>
       </c>
       <c r="T103" t="n">
-        <v>255040</v>
+        <v>219200</v>
       </c>
       <c r="U103" t="n">
         <v>160000</v>
       </c>
       <c r="V103" t="n">
-        <v>95040</v>
+        <v>59200</v>
       </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
@@ -14023,10 +14023,10 @@
         <v>1324720</v>
       </c>
       <c r="U106" t="n">
-        <v>1289000</v>
+        <v>1090400</v>
       </c>
       <c r="V106" t="n">
-        <v>35720</v>
+        <v>234320</v>
       </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-29.xlsx
@@ -14204,7 +14204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14714,6 +14714,36 @@
         </is>
       </c>
       <c r="F17" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -15745,7 +15775,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "지급상태": "미지급", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>
